--- a/商品マスター.xlsx
+++ b/商品マスター.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codex用カタログ元データ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanei004\Documents\GitHub\sanei-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEBFDC1-D910-466C-8264-E311FFA6844B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A68549B-17A9-4057-8F51-7C006AEEFB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="29415" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="商品マスター" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2821" uniqueCount="1306">
   <si>
     <t>自社コード</t>
   </si>
@@ -3939,6 +3939,19 @@
   </si>
   <si>
     <t>01808157</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一時代替品での提案になります</t>
+    <rPh sb="0" eb="2">
+      <t>イチジ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ダイタイヒン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テイアン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3986,10 +3999,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -13763,6 +13777,9 @@
       <c r="K260" t="s">
         <v>22</v>
       </c>
+      <c r="M260" s="3" t="s">
+        <v>1305</v>
+      </c>
       <c r="N260" t="s">
         <v>1150</v>
       </c>

--- a/商品マスター.xlsx
+++ b/商品マスター.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanei004\Documents\GitHub\sanei-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257A6270-38DB-4672-92A8-364A651107F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7FA65D-0780-4500-B6FE-34ED29C7D582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="495" windowWidth="28485" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="285" windowWidth="28485" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="商品マスター" sheetId="1" r:id="rId1"/>
@@ -3800,12 +3800,6 @@
     <t>00900352</t>
   </si>
   <si>
-    <t>ゆず大根(150g)ﾊﾞﾗ</t>
-  </si>
-  <si>
-    <t>ゆずだいこん150</t>
-  </si>
-  <si>
     <t>D+16日</t>
   </si>
   <si>
@@ -3846,9 +3840,6 @@
   </si>
   <si>
     <t>D+20日</t>
-  </si>
-  <si>
-    <t>00901208</t>
   </si>
   <si>
     <t>野沢菜ｷｬﾍﾞﾂわさび風味[150g]</t>
@@ -4443,6 +4434,18 @@
   </si>
   <si>
     <t>02104770</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆず大根(220g)ﾊﾞﾗ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゆずだいこん220</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00901208</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4793,7 +4796,7 @@
         <v>23</v>
       </c>
       <c r="O2" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P2">
         <v>6900</v>
@@ -4828,7 +4831,7 @@
         <v>30</v>
       </c>
       <c r="O3" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="P3">
         <v>2900</v>
@@ -4863,7 +4866,7 @@
         <v>30</v>
       </c>
       <c r="O4" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="P4">
         <v>2900</v>
@@ -4898,7 +4901,7 @@
         <v>30</v>
       </c>
       <c r="O5" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P5">
         <v>6200</v>
@@ -4933,7 +4936,7 @@
         <v>30</v>
       </c>
       <c r="O6" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P6">
         <v>6900</v>
@@ -4971,7 +4974,7 @@
         <v>30</v>
       </c>
       <c r="O7" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P7">
         <v>6900</v>
@@ -5076,7 +5079,7 @@
         <v>62</v>
       </c>
       <c r="O10" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="P10">
         <v>7800</v>
@@ -5114,7 +5117,7 @@
         <v>68</v>
       </c>
       <c r="O11" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P11">
         <v>3100</v>
@@ -5149,7 +5152,7 @@
         <v>68</v>
       </c>
       <c r="O12" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P12">
         <v>4700</v>
@@ -5181,7 +5184,7 @@
         <v>68</v>
       </c>
       <c r="O13" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P13">
         <v>6200</v>
@@ -5216,7 +5219,7 @@
         <v>68</v>
       </c>
       <c r="O14" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P14">
         <v>4700</v>
@@ -5251,7 +5254,7 @@
         <v>68</v>
       </c>
       <c r="O15" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P15">
         <v>4700</v>
@@ -5286,7 +5289,7 @@
         <v>68</v>
       </c>
       <c r="O16" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P16">
         <v>6000</v>
@@ -5321,7 +5324,7 @@
         <v>95</v>
       </c>
       <c r="O17" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P17">
         <v>6700</v>
@@ -5359,7 +5362,7 @@
         <v>95</v>
       </c>
       <c r="O18" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="P18">
         <v>1400</v>
@@ -5394,7 +5397,7 @@
         <v>105</v>
       </c>
       <c r="O19" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P19">
         <v>3100</v>
@@ -5429,7 +5432,7 @@
         <v>110</v>
       </c>
       <c r="O20" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P20">
         <v>900</v>
@@ -5464,7 +5467,7 @@
         <v>110</v>
       </c>
       <c r="O21" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P21">
         <v>900</v>
@@ -5502,7 +5505,7 @@
         <v>110</v>
       </c>
       <c r="O22" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P22">
         <v>900</v>
@@ -5540,7 +5543,7 @@
         <v>110</v>
       </c>
       <c r="O23" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P23">
         <v>900</v>
@@ -5575,7 +5578,7 @@
         <v>110</v>
       </c>
       <c r="O24" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P24">
         <v>3000</v>
@@ -5616,7 +5619,7 @@
         <v>110</v>
       </c>
       <c r="O25" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="P25">
         <v>4600</v>
@@ -5654,7 +5657,7 @@
         <v>110</v>
       </c>
       <c r="O26" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P26">
         <v>6200</v>
@@ -5692,7 +5695,7 @@
         <v>110</v>
       </c>
       <c r="O27" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P27">
         <v>4900</v>
@@ -5727,7 +5730,7 @@
         <v>110</v>
       </c>
       <c r="O28" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P28">
         <v>7200</v>
@@ -5762,7 +5765,7 @@
         <v>110</v>
       </c>
       <c r="O29" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P29">
         <v>6400</v>
@@ -5800,7 +5803,7 @@
         <v>110</v>
       </c>
       <c r="O30" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="P30">
         <v>2300</v>
@@ -5838,7 +5841,7 @@
         <v>110</v>
       </c>
       <c r="O31" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="P31">
         <v>7800</v>
@@ -5873,7 +5876,7 @@
         <v>165</v>
       </c>
       <c r="O32" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P32">
         <v>6400</v>
@@ -5908,7 +5911,7 @@
         <v>165</v>
       </c>
       <c r="O33" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P33">
         <v>6400</v>
@@ -6016,7 +6019,7 @@
         <v>182</v>
       </c>
       <c r="O36" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="P36">
         <v>5400</v>
@@ -6051,7 +6054,7 @@
         <v>186</v>
       </c>
       <c r="O37" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P37">
         <v>4700</v>
@@ -6086,7 +6089,7 @@
         <v>186</v>
       </c>
       <c r="O38" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P38">
         <v>4700</v>
@@ -6121,7 +6124,7 @@
         <v>186</v>
       </c>
       <c r="O39" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P39">
         <v>4700</v>
@@ -6191,7 +6194,7 @@
         <v>203</v>
       </c>
       <c r="O41" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P41">
         <v>3100</v>
@@ -6226,7 +6229,7 @@
         <v>203</v>
       </c>
       <c r="O42" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P42">
         <v>3100</v>
@@ -6261,7 +6264,7 @@
         <v>203</v>
       </c>
       <c r="O43" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P43">
         <v>3000</v>
@@ -6299,7 +6302,7 @@
         <v>215</v>
       </c>
       <c r="O44" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="P44">
         <v>200</v>
@@ -6334,7 +6337,7 @@
         <v>215</v>
       </c>
       <c r="O45" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P45">
         <v>3000</v>
@@ -6369,7 +6372,7 @@
         <v>215</v>
       </c>
       <c r="O46" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P46">
         <v>3000</v>
@@ -6404,7 +6407,7 @@
         <v>215</v>
       </c>
       <c r="O47" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P47">
         <v>3100</v>
@@ -6445,7 +6448,7 @@
         <v>215</v>
       </c>
       <c r="O48" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P48">
         <v>4900</v>
@@ -6483,7 +6486,7 @@
         <v>215</v>
       </c>
       <c r="O49" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P49">
         <v>6400</v>
@@ -6521,7 +6524,7 @@
         <v>215</v>
       </c>
       <c r="O50" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P50">
         <v>900</v>
@@ -6556,7 +6559,7 @@
         <v>245</v>
       </c>
       <c r="O51" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="P51">
         <v>4500</v>
@@ -6591,7 +6594,7 @@
         <v>250</v>
       </c>
       <c r="O52" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P52">
         <v>4700</v>
@@ -6629,7 +6632,7 @@
         <v>250</v>
       </c>
       <c r="O53" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P53">
         <v>4700</v>
@@ -6667,7 +6670,7 @@
         <v>250</v>
       </c>
       <c r="O54" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P54">
         <v>4700</v>
@@ -6705,7 +6708,7 @@
         <v>250</v>
       </c>
       <c r="O55" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P55">
         <v>4700</v>
@@ -6743,7 +6746,7 @@
         <v>267</v>
       </c>
       <c r="O56" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="P56">
         <v>7300</v>
@@ -6778,7 +6781,7 @@
         <v>272</v>
       </c>
       <c r="O57" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P57">
         <v>3000</v>
@@ -6883,7 +6886,7 @@
         <v>285</v>
       </c>
       <c r="O60" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="P60">
         <v>6800</v>
@@ -6918,7 +6921,7 @@
         <v>290</v>
       </c>
       <c r="O61" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P61">
         <v>6900</v>
@@ -6956,7 +6959,7 @@
         <v>294</v>
       </c>
       <c r="O62" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="P62">
         <v>300</v>
@@ -6994,7 +6997,7 @@
         <v>294</v>
       </c>
       <c r="O63" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P63">
         <v>900</v>
@@ -7032,7 +7035,7 @@
         <v>294</v>
       </c>
       <c r="O64" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P64">
         <v>900</v>
@@ -7073,7 +7076,7 @@
         <v>294</v>
       </c>
       <c r="O65" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P65">
         <v>900</v>
@@ -7108,7 +7111,7 @@
         <v>294</v>
       </c>
       <c r="O66" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P66">
         <v>900</v>
@@ -7146,7 +7149,7 @@
         <v>294</v>
       </c>
       <c r="O67" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P67">
         <v>5000</v>
@@ -7187,7 +7190,7 @@
         <v>294</v>
       </c>
       <c r="O68" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P68">
         <v>6000</v>
@@ -7225,7 +7228,7 @@
         <v>294</v>
       </c>
       <c r="O69" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P69">
         <v>6000</v>
@@ -7260,7 +7263,7 @@
         <v>327</v>
       </c>
       <c r="O70" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P70">
         <v>5000</v>
@@ -7295,7 +7298,7 @@
         <v>327</v>
       </c>
       <c r="O71" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P71">
         <v>5000</v>
@@ -7330,7 +7333,7 @@
         <v>335</v>
       </c>
       <c r="O72" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="P72">
         <v>3300</v>
@@ -7365,7 +7368,7 @@
         <v>335</v>
       </c>
       <c r="O73" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="P73">
         <v>3300</v>
@@ -7400,7 +7403,7 @@
         <v>342</v>
       </c>
       <c r="O74" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P74">
         <v>5100</v>
@@ -7435,7 +7438,7 @@
         <v>346</v>
       </c>
       <c r="O75" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P75">
         <v>6700</v>
@@ -7470,7 +7473,7 @@
         <v>346</v>
       </c>
       <c r="O76" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P76">
         <v>6700</v>
@@ -7505,7 +7508,7 @@
         <v>346</v>
       </c>
       <c r="O77" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P77">
         <v>6700</v>
@@ -7540,7 +7543,7 @@
         <v>346</v>
       </c>
       <c r="O78" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P78">
         <v>6700</v>
@@ -7578,7 +7581,7 @@
         <v>346</v>
       </c>
       <c r="O79" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P79">
         <v>6700</v>
@@ -7613,7 +7616,7 @@
         <v>346</v>
       </c>
       <c r="O80" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="P80">
         <v>6700</v>
@@ -7648,7 +7651,7 @@
         <v>368</v>
       </c>
       <c r="O81" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P81">
         <v>7100</v>
@@ -7686,7 +7689,7 @@
         <v>374</v>
       </c>
       <c r="O82" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P82">
         <v>100</v>
@@ -7724,7 +7727,7 @@
         <v>374</v>
       </c>
       <c r="O83" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P83">
         <v>100</v>
@@ -7762,7 +7765,7 @@
         <v>374</v>
       </c>
       <c r="O84" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P84">
         <v>100</v>
@@ -7800,7 +7803,7 @@
         <v>374</v>
       </c>
       <c r="O85" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P85">
         <v>100</v>
@@ -7838,7 +7841,7 @@
         <v>374</v>
       </c>
       <c r="O86" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P86">
         <v>100</v>
@@ -7873,7 +7876,7 @@
         <v>395</v>
       </c>
       <c r="O87" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P87">
         <v>3000</v>
@@ -7908,7 +7911,7 @@
         <v>395</v>
       </c>
       <c r="O88" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="P88">
         <v>2600</v>
@@ -7943,7 +7946,7 @@
         <v>395</v>
       </c>
       <c r="O89" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="P89">
         <v>5800</v>
@@ -7975,7 +7978,7 @@
         <v>395</v>
       </c>
       <c r="O90" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P90">
         <v>3000</v>
@@ -8013,7 +8016,7 @@
         <v>409</v>
       </c>
       <c r="O91" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P91">
         <v>7600</v>
@@ -8048,7 +8051,7 @@
         <v>413</v>
       </c>
       <c r="O92" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P92">
         <v>5100</v>
@@ -8083,7 +8086,7 @@
         <v>413</v>
       </c>
       <c r="O93" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P93">
         <v>5100</v>
@@ -8118,7 +8121,7 @@
         <v>413</v>
       </c>
       <c r="O94" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P94">
         <v>5100</v>
@@ -8153,7 +8156,7 @@
         <v>413</v>
       </c>
       <c r="O95" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P95">
         <v>5100</v>
@@ -8191,7 +8194,7 @@
         <v>413</v>
       </c>
       <c r="O96" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P96">
         <v>5100</v>
@@ -8226,7 +8229,7 @@
         <v>413</v>
       </c>
       <c r="O97" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P97">
         <v>5100</v>
@@ -8261,7 +8264,7 @@
         <v>413</v>
       </c>
       <c r="O98" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P98">
         <v>5100</v>
@@ -8299,7 +8302,7 @@
         <v>413</v>
       </c>
       <c r="O99" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P99">
         <v>5100</v>
@@ -8334,7 +8337,7 @@
         <v>413</v>
       </c>
       <c r="O100" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P100">
         <v>5100</v>
@@ -8369,7 +8372,7 @@
         <v>413</v>
       </c>
       <c r="O101" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P101">
         <v>5100</v>
@@ -8404,7 +8407,7 @@
         <v>413</v>
       </c>
       <c r="O102" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P102">
         <v>5100</v>
@@ -8439,7 +8442,7 @@
         <v>413</v>
       </c>
       <c r="O103" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P103">
         <v>5100</v>
@@ -8474,7 +8477,7 @@
         <v>413</v>
       </c>
       <c r="O104" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P104">
         <v>5100</v>
@@ -8509,7 +8512,7 @@
         <v>413</v>
       </c>
       <c r="O105" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P105">
         <v>5100</v>
@@ -8549,7 +8552,7 @@
         <v>413</v>
       </c>
       <c r="O106" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P106">
         <v>5100</v>
@@ -8800,7 +8803,7 @@
         <v>490</v>
       </c>
       <c r="O113" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P113">
         <v>600</v>
@@ -8838,7 +8841,7 @@
         <v>495</v>
       </c>
       <c r="O114" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P114">
         <v>7600</v>
@@ -8876,7 +8879,7 @@
         <v>495</v>
       </c>
       <c r="O115" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P115">
         <v>7600</v>
@@ -8914,7 +8917,7 @@
         <v>495</v>
       </c>
       <c r="O116" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P116">
         <v>7600</v>
@@ -8952,7 +8955,7 @@
         <v>495</v>
       </c>
       <c r="O117" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="P117">
         <v>7600</v>
@@ -8990,7 +8993,7 @@
         <v>513</v>
       </c>
       <c r="O118" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P118">
         <v>5100</v>
@@ -9025,7 +9028,7 @@
         <v>513</v>
       </c>
       <c r="O119" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P119">
         <v>5100</v>
@@ -9060,7 +9063,7 @@
         <v>513</v>
       </c>
       <c r="O120" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P120">
         <v>5100</v>
@@ -9095,7 +9098,7 @@
         <v>513</v>
       </c>
       <c r="O121" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P121">
         <v>5100</v>
@@ -9130,7 +9133,7 @@
         <v>513</v>
       </c>
       <c r="O122" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P122">
         <v>5100</v>
@@ -9165,7 +9168,7 @@
         <v>531</v>
       </c>
       <c r="O123" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P123">
         <v>4700</v>
@@ -9203,7 +9206,7 @@
         <v>531</v>
       </c>
       <c r="O124" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P124">
         <v>4700</v>
@@ -9238,7 +9241,7 @@
         <v>531</v>
       </c>
       <c r="O125" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P125">
         <v>4700</v>
@@ -9273,7 +9276,7 @@
         <v>531</v>
       </c>
       <c r="O126" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P126">
         <v>4700</v>
@@ -9308,7 +9311,7 @@
         <v>531</v>
       </c>
       <c r="O127" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P127">
         <v>4700</v>
@@ -9346,7 +9349,7 @@
         <v>553</v>
       </c>
       <c r="O128" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P128">
         <v>600</v>
@@ -9381,7 +9384,7 @@
         <v>553</v>
       </c>
       <c r="O129" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P129">
         <v>4700</v>
@@ -9416,7 +9419,7 @@
         <v>553</v>
       </c>
       <c r="O130" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="P130">
         <v>7300</v>
@@ -9454,7 +9457,7 @@
         <v>553</v>
       </c>
       <c r="O131" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P131">
         <v>4000</v>
@@ -9591,7 +9594,7 @@
         <v>581</v>
       </c>
       <c r="O135" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="P135">
         <v>4500</v>
@@ -9801,7 +9804,7 @@
         <v>603</v>
       </c>
       <c r="O141" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P141">
         <v>600</v>
@@ -9839,7 +9842,7 @@
         <v>603</v>
       </c>
       <c r="O142" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="P142">
         <v>1700</v>
@@ -9874,7 +9877,7 @@
         <v>603</v>
       </c>
       <c r="O143" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="P143">
         <v>4600</v>
@@ -9909,7 +9912,7 @@
         <v>603</v>
       </c>
       <c r="O144" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="P144">
         <v>4600</v>
@@ -9944,7 +9947,7 @@
         <v>603</v>
       </c>
       <c r="O145" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P145">
         <v>4700</v>
@@ -9979,7 +9982,7 @@
         <v>603</v>
       </c>
       <c r="O146" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P146">
         <v>5000</v>
@@ -10014,7 +10017,7 @@
         <v>603</v>
       </c>
       <c r="O147" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P147">
         <v>5000</v>
@@ -10049,7 +10052,7 @@
         <v>603</v>
       </c>
       <c r="O148" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="P148">
         <v>8000</v>
@@ -10087,7 +10090,7 @@
         <v>603</v>
       </c>
       <c r="O149" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="P149">
         <v>8000</v>
@@ -10122,7 +10125,7 @@
         <v>603</v>
       </c>
       <c r="O150" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="P150">
         <v>8000</v>
@@ -10157,7 +10160,7 @@
         <v>641</v>
       </c>
       <c r="O151" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="P151">
         <v>5800</v>
@@ -10192,7 +10195,7 @@
         <v>641</v>
       </c>
       <c r="O152" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="P152">
         <v>5800</v>
@@ -10227,7 +10230,7 @@
         <v>641</v>
       </c>
       <c r="O153" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="P153">
         <v>5800</v>
@@ -10262,7 +10265,7 @@
         <v>641</v>
       </c>
       <c r="O154" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="P154">
         <v>5800</v>
@@ -10297,7 +10300,7 @@
         <v>641</v>
       </c>
       <c r="O155" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="P155">
         <v>3900</v>
@@ -10332,7 +10335,7 @@
         <v>641</v>
       </c>
       <c r="O156" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="P156">
         <v>2600</v>
@@ -10367,7 +10370,7 @@
         <v>641</v>
       </c>
       <c r="O157" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="P157">
         <v>2600</v>
@@ -10402,7 +10405,7 @@
         <v>641</v>
       </c>
       <c r="O158" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P158">
         <v>4000</v>
@@ -10437,7 +10440,7 @@
         <v>641</v>
       </c>
       <c r="O159" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P159">
         <v>4000</v>
@@ -10472,7 +10475,7 @@
         <v>641</v>
       </c>
       <c r="O160" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P160">
         <v>4000</v>
@@ -10507,7 +10510,7 @@
         <v>641</v>
       </c>
       <c r="O161" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P161">
         <v>4000</v>
@@ -10545,7 +10548,7 @@
         <v>641</v>
       </c>
       <c r="O162" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P162">
         <v>4000</v>
@@ -10580,7 +10583,7 @@
         <v>641</v>
       </c>
       <c r="O163" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P163">
         <v>4000</v>
@@ -10615,7 +10618,7 @@
         <v>641</v>
       </c>
       <c r="O164" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P164">
         <v>4000</v>
@@ -10650,7 +10653,7 @@
         <v>641</v>
       </c>
       <c r="O165" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P165">
         <v>4000</v>
@@ -10685,7 +10688,7 @@
         <v>641</v>
       </c>
       <c r="O166" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="P166">
         <v>4000</v>
@@ -10720,7 +10723,7 @@
         <v>641</v>
       </c>
       <c r="O167" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="P167">
         <v>4100</v>
@@ -10755,7 +10758,7 @@
         <v>641</v>
       </c>
       <c r="O168" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="P168">
         <v>4100</v>
@@ -10790,7 +10793,7 @@
         <v>705</v>
       </c>
       <c r="O169" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P169">
         <v>3000</v>
@@ -10825,7 +10828,7 @@
         <v>705</v>
       </c>
       <c r="O170" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P170">
         <v>3000</v>
@@ -10860,7 +10863,7 @@
         <v>705</v>
       </c>
       <c r="O171" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P171">
         <v>3000</v>
@@ -10895,7 +10898,7 @@
         <v>705</v>
       </c>
       <c r="O172" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P172">
         <v>3000</v>
@@ -10930,7 +10933,7 @@
         <v>720</v>
       </c>
       <c r="O173" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="P173">
         <v>5600</v>
@@ -10965,7 +10968,7 @@
         <v>720</v>
       </c>
       <c r="O174" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="P174">
         <v>5600</v>
@@ -11003,7 +11006,7 @@
         <v>729</v>
       </c>
       <c r="O175" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P175">
         <v>4700</v>
@@ -11038,7 +11041,7 @@
         <v>729</v>
       </c>
       <c r="O176" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P176">
         <v>4700</v>
@@ -11079,7 +11082,7 @@
         <v>739</v>
       </c>
       <c r="O177" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="P177">
         <v>100</v>
@@ -11120,7 +11123,7 @@
         <v>739</v>
       </c>
       <c r="O178" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P178">
         <v>600</v>
@@ -11161,7 +11164,7 @@
         <v>739</v>
       </c>
       <c r="O179" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="P179">
         <v>2400</v>
@@ -11196,7 +11199,7 @@
         <v>739</v>
       </c>
       <c r="O180" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="P180">
         <v>2400</v>
@@ -11234,7 +11237,7 @@
         <v>739</v>
       </c>
       <c r="O181" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P181">
         <v>3000</v>
@@ -11275,7 +11278,7 @@
         <v>739</v>
       </c>
       <c r="O182" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P182">
         <v>3000</v>
@@ -11313,7 +11316,7 @@
         <v>739</v>
       </c>
       <c r="O183" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P183">
         <v>3000</v>
@@ -11351,7 +11354,7 @@
         <v>739</v>
       </c>
       <c r="O184" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P184">
         <v>3000</v>
@@ -11392,7 +11395,7 @@
         <v>739</v>
       </c>
       <c r="O185" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="P185">
         <v>3100</v>
@@ -11433,7 +11436,7 @@
         <v>739</v>
       </c>
       <c r="O186" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P186">
         <v>5100</v>
@@ -11471,7 +11474,7 @@
         <v>739</v>
       </c>
       <c r="O187" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="P187">
         <v>5100</v>
@@ -11512,7 +11515,7 @@
         <v>739</v>
       </c>
       <c r="O188" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="P188">
         <v>4600</v>
@@ -11553,7 +11556,7 @@
         <v>739</v>
       </c>
       <c r="O189" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="P189">
         <v>4600</v>
@@ -11591,7 +11594,7 @@
         <v>739</v>
       </c>
       <c r="O190" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P190">
         <v>6200</v>
@@ -11626,7 +11629,7 @@
         <v>739</v>
       </c>
       <c r="O191" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P191">
         <v>4900</v>
@@ -11667,7 +11670,7 @@
         <v>739</v>
       </c>
       <c r="O192" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P192">
         <v>5000</v>
@@ -11705,7 +11708,7 @@
         <v>739</v>
       </c>
       <c r="O193" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P193">
         <v>5000</v>
@@ -11743,7 +11746,7 @@
         <v>739</v>
       </c>
       <c r="O194" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P194">
         <v>5000</v>
@@ -11784,7 +11787,7 @@
         <v>739</v>
       </c>
       <c r="O195" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P195">
         <v>5000</v>
@@ -11825,7 +11828,7 @@
         <v>739</v>
       </c>
       <c r="O196" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P196">
         <v>5000</v>
@@ -11863,7 +11866,7 @@
         <v>739</v>
       </c>
       <c r="O197" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P197">
         <v>6200</v>
@@ -11904,7 +11907,7 @@
         <v>739</v>
       </c>
       <c r="O198" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P198">
         <v>6200</v>
@@ -11945,7 +11948,7 @@
         <v>739</v>
       </c>
       <c r="O199" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P199">
         <v>6200</v>
@@ -11983,7 +11986,7 @@
         <v>739</v>
       </c>
       <c r="O200" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P200">
         <v>6200</v>
@@ -12021,7 +12024,7 @@
         <v>739</v>
       </c>
       <c r="O201" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P201">
         <v>6200</v>
@@ -12062,7 +12065,7 @@
         <v>739</v>
       </c>
       <c r="O202" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="P202">
         <v>6300</v>
@@ -12100,7 +12103,7 @@
         <v>739</v>
       </c>
       <c r="O203" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="P203">
         <v>6300</v>
@@ -12138,7 +12141,7 @@
         <v>739</v>
       </c>
       <c r="O204" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P204">
         <v>6400</v>
@@ -12173,7 +12176,7 @@
         <v>739</v>
       </c>
       <c r="O205" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P205">
         <v>6600</v>
@@ -12211,7 +12214,7 @@
         <v>739</v>
       </c>
       <c r="O206" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P206">
         <v>6600</v>
@@ -12249,7 +12252,7 @@
         <v>739</v>
       </c>
       <c r="O207" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P207">
         <v>6900</v>
@@ -12287,7 +12290,7 @@
         <v>739</v>
       </c>
       <c r="O208" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P208">
         <v>6900</v>
@@ -12328,7 +12331,7 @@
         <v>739</v>
       </c>
       <c r="O209" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="P209">
         <v>6900</v>
@@ -12369,7 +12372,7 @@
         <v>739</v>
       </c>
       <c r="O210" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="P210">
         <v>8000</v>
@@ -12404,7 +12407,7 @@
         <v>739</v>
       </c>
       <c r="O211" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="P211">
         <v>7500</v>
@@ -12442,7 +12445,7 @@
         <v>739</v>
       </c>
       <c r="O212" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P212">
         <v>3000</v>
@@ -12480,7 +12483,7 @@
         <v>739</v>
       </c>
       <c r="O213" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P213">
         <v>3000</v>
@@ -12518,7 +12521,7 @@
         <v>739</v>
       </c>
       <c r="O214" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="P214">
         <v>3000</v>
@@ -12553,7 +12556,7 @@
         <v>739</v>
       </c>
       <c r="O215" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="P215">
         <v>3600</v>
@@ -12591,7 +12594,7 @@
         <v>739</v>
       </c>
       <c r="O216" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="P216">
         <v>6200</v>
@@ -12629,7 +12632,7 @@
         <v>739</v>
       </c>
       <c r="O217" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="P217">
         <v>1000</v>
@@ -12664,7 +12667,7 @@
         <v>739</v>
       </c>
       <c r="O218" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="P218">
         <v>4700</v>
@@ -12702,7 +12705,7 @@
         <v>739</v>
       </c>
       <c r="O219" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P219">
         <v>4900</v>
@@ -12743,7 +12746,7 @@
         <v>739</v>
       </c>
       <c r="O220" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="P220">
         <v>5000</v>
@@ -12930,7 +12933,7 @@
         <v>739</v>
       </c>
       <c r="O225" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P225">
         <v>7200</v>
@@ -12968,7 +12971,7 @@
         <v>739</v>
       </c>
       <c r="O226" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P226">
         <v>7200</v>
@@ -13003,7 +13006,7 @@
         <v>739</v>
       </c>
       <c r="O227" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P227">
         <v>7200</v>
@@ -13038,7 +13041,7 @@
         <v>739</v>
       </c>
       <c r="O228" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P228">
         <v>7200</v>
@@ -13076,7 +13079,7 @@
         <v>739</v>
       </c>
       <c r="O229" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P229">
         <v>7200</v>
@@ -13117,7 +13120,7 @@
         <v>739</v>
       </c>
       <c r="O230" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P230">
         <v>7200</v>
@@ -13152,7 +13155,7 @@
         <v>739</v>
       </c>
       <c r="O231" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P231">
         <v>7200</v>
@@ -13187,7 +13190,7 @@
         <v>739</v>
       </c>
       <c r="O232" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P232">
         <v>7200</v>
@@ -13225,7 +13228,7 @@
         <v>739</v>
       </c>
       <c r="O233" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P233">
         <v>7200</v>
@@ -13260,7 +13263,7 @@
         <v>739</v>
       </c>
       <c r="O234" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="P234">
         <v>7200</v>
@@ -13298,7 +13301,7 @@
         <v>739</v>
       </c>
       <c r="O235" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="P235">
         <v>6100</v>
@@ -13339,7 +13342,7 @@
         <v>739</v>
       </c>
       <c r="O236" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="P236">
         <v>6100</v>
@@ -13380,7 +13383,7 @@
         <v>739</v>
       </c>
       <c r="O237" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P237">
         <v>6400</v>
@@ -13421,7 +13424,7 @@
         <v>739</v>
       </c>
       <c r="O238" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="P238">
         <v>6500</v>
@@ -13456,7 +13459,7 @@
         <v>739</v>
       </c>
       <c r="O239" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P239">
         <v>600</v>
@@ -13497,7 +13500,7 @@
         <v>739</v>
       </c>
       <c r="O240" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P240">
         <v>600</v>
@@ -13538,7 +13541,7 @@
         <v>739</v>
       </c>
       <c r="O241" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="P241">
         <v>6400</v>
@@ -13579,7 +13582,7 @@
         <v>739</v>
       </c>
       <c r="O242" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="P242">
         <v>2400</v>
@@ -13620,7 +13623,7 @@
         <v>739</v>
       </c>
       <c r="O243" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="P243">
         <v>2000</v>
@@ -13661,7 +13664,7 @@
         <v>739</v>
       </c>
       <c r="O244" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="P244">
         <v>5400</v>
@@ -13699,7 +13702,7 @@
         <v>739</v>
       </c>
       <c r="O245" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="P245">
         <v>5400</v>
@@ -13737,7 +13740,7 @@
         <v>739</v>
       </c>
       <c r="O246" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="P246">
         <v>5400</v>
@@ -13775,7 +13778,7 @@
         <v>739</v>
       </c>
       <c r="O247" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="P247">
         <v>5400</v>
@@ -13816,7 +13819,7 @@
         <v>739</v>
       </c>
       <c r="O248" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P248">
         <v>6000</v>
@@ -13857,7 +13860,7 @@
         <v>739</v>
       </c>
       <c r="O249" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P249">
         <v>6000</v>
@@ -13898,7 +13901,7 @@
         <v>739</v>
       </c>
       <c r="O250" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P250">
         <v>6000</v>
@@ -13939,7 +13942,7 @@
         <v>739</v>
       </c>
       <c r="O251" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P251">
         <v>6000</v>
@@ -13980,7 +13983,7 @@
         <v>739</v>
       </c>
       <c r="O252" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P252">
         <v>6000</v>
@@ -14021,7 +14024,7 @@
         <v>739</v>
       </c>
       <c r="O253" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P253">
         <v>6000</v>
@@ -14062,7 +14065,7 @@
         <v>739</v>
       </c>
       <c r="O254" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P254">
         <v>6000</v>
@@ -14103,7 +14106,7 @@
         <v>739</v>
       </c>
       <c r="O255" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="P255">
         <v>6000</v>
@@ -14138,7 +14141,7 @@
         <v>1095</v>
       </c>
       <c r="O256" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P256">
         <v>4900</v>
@@ -14176,7 +14179,7 @@
         <v>1095</v>
       </c>
       <c r="O257" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P257">
         <v>4900</v>
@@ -14211,7 +14214,7 @@
         <v>1095</v>
       </c>
       <c r="O258" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P258">
         <v>4900</v>
@@ -14246,7 +14249,7 @@
         <v>1095</v>
       </c>
       <c r="O259" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="P259">
         <v>4900</v>
@@ -14281,7 +14284,7 @@
         <v>1110</v>
       </c>
       <c r="O260" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="P260">
         <v>2500</v>
@@ -14319,7 +14322,7 @@
         <v>1110</v>
       </c>
       <c r="O261" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="P261">
         <v>2500</v>
@@ -14354,7 +14357,7 @@
         <v>1119</v>
       </c>
       <c r="O262" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="P262">
         <v>3400</v>
@@ -14392,7 +14395,7 @@
         <v>1119</v>
       </c>
       <c r="O263" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="P263">
         <v>3400</v>
@@ -14430,7 +14433,7 @@
         <v>1119</v>
       </c>
       <c r="O264" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="P264">
         <v>3500</v>
@@ -14465,7 +14468,7 @@
         <v>1119</v>
       </c>
       <c r="O265" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="P265">
         <v>3500</v>
@@ -14503,7 +14506,7 @@
         <v>1119</v>
       </c>
       <c r="O266" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="P266">
         <v>3500</v>
@@ -14538,7 +14541,7 @@
         <v>1119</v>
       </c>
       <c r="O267" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="P267">
         <v>3500</v>
@@ -14611,7 +14614,7 @@
         <v>1147</v>
       </c>
       <c r="O269" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="P269">
         <v>200</v>
@@ -14646,7 +14649,7 @@
         <v>1147</v>
       </c>
       <c r="O270" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="P270">
         <v>600</v>
@@ -14681,7 +14684,7 @@
         <v>1147</v>
       </c>
       <c r="O271" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P271">
         <v>900</v>
@@ -14716,7 +14719,7 @@
         <v>1147</v>
       </c>
       <c r="O272" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P272">
         <v>900</v>
@@ -14751,7 +14754,7 @@
         <v>1147</v>
       </c>
       <c r="O273" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="P273">
         <v>900</v>
@@ -14786,7 +14789,7 @@
         <v>1147</v>
       </c>
       <c r="O274" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="P274">
         <v>1000</v>
@@ -14821,7 +14824,7 @@
         <v>1147</v>
       </c>
       <c r="O275" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="P275">
         <v>1100</v>
@@ -14856,7 +14859,7 @@
         <v>1147</v>
       </c>
       <c r="O276" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="P276">
         <v>1100</v>
@@ -14891,7 +14894,7 @@
         <v>1147</v>
       </c>
       <c r="O277" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="P277">
         <v>1100</v>
@@ -14926,7 +14929,7 @@
         <v>1147</v>
       </c>
       <c r="O278" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="P278">
         <v>1400</v>
@@ -14964,7 +14967,7 @@
         <v>1147</v>
       </c>
       <c r="O279" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="P279">
         <v>1300</v>
@@ -15034,7 +15037,7 @@
         <v>1191</v>
       </c>
       <c r="O281" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="P281">
         <v>3700</v>
@@ -15042,16 +15045,16 @@
     </row>
     <row r="282" spans="1:16">
       <c r="A282" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F282" s="3" t="s">
         <v>1460</v>
-      </c>
-      <c r="D282" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>1462</v>
-      </c>
-      <c r="F282" s="3" t="s">
-        <v>1463</v>
       </c>
       <c r="H282" t="s">
         <v>28</v>
@@ -15069,7 +15072,7 @@
         <v>1192</v>
       </c>
       <c r="O282" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="P282">
         <v>2800</v>
@@ -15077,16 +15080,16 @@
     </row>
     <row r="283" spans="1:16">
       <c r="A283" s="2" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="D283" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="H283" t="s">
         <v>28</v>
@@ -15104,7 +15107,7 @@
         <v>1192</v>
       </c>
       <c r="O283" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="P283">
         <v>2800</v>
@@ -15112,16 +15115,16 @@
     </row>
     <row r="284" spans="1:16">
       <c r="A284" s="2" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="B284">
         <v>100097</v>
       </c>
       <c r="D284" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F284" t="s">
         <v>41</v>
@@ -15142,7 +15145,7 @@
         <v>1192</v>
       </c>
       <c r="O284" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="P284">
         <v>3300</v>
@@ -15177,7 +15180,7 @@
         <v>1192</v>
       </c>
       <c r="O285" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="P285">
         <v>3300</v>
@@ -15212,7 +15215,7 @@
         <v>1192</v>
       </c>
       <c r="O286" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="P286">
         <v>3600</v>
@@ -15247,7 +15250,7 @@
         <v>1192</v>
       </c>
       <c r="O287" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="P287">
         <v>3600</v>
@@ -15282,7 +15285,7 @@
         <v>1192</v>
       </c>
       <c r="O288" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="P288">
         <v>2900</v>
@@ -15317,7 +15320,7 @@
         <v>1192</v>
       </c>
       <c r="O289" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="P289">
         <v>3600</v>
@@ -15352,7 +15355,7 @@
         <v>1213</v>
       </c>
       <c r="O290" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="P290">
         <v>7400</v>
@@ -15387,7 +15390,7 @@
         <v>1218</v>
       </c>
       <c r="O291" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P291">
         <v>6600</v>
@@ -15422,7 +15425,7 @@
         <v>1218</v>
       </c>
       <c r="O292" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P292">
         <v>6600</v>
@@ -15457,7 +15460,7 @@
         <v>1218</v>
       </c>
       <c r="O293" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P293">
         <v>6600</v>
@@ -15492,7 +15495,7 @@
         <v>1218</v>
       </c>
       <c r="O294" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P294">
         <v>6600</v>
@@ -15527,7 +15530,7 @@
         <v>1218</v>
       </c>
       <c r="O295" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P295">
         <v>6600</v>
@@ -15562,7 +15565,7 @@
         <v>1218</v>
       </c>
       <c r="O296" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P296">
         <v>6600</v>
@@ -15597,7 +15600,7 @@
         <v>1218</v>
       </c>
       <c r="O297" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P297">
         <v>6600</v>
@@ -15632,7 +15635,7 @@
         <v>1218</v>
       </c>
       <c r="O298" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P298">
         <v>6600</v>
@@ -15667,7 +15670,7 @@
         <v>1218</v>
       </c>
       <c r="O299" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P299">
         <v>6600</v>
@@ -15702,7 +15705,7 @@
         <v>1218</v>
       </c>
       <c r="O300" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P300">
         <v>6600</v>
@@ -15737,7 +15740,7 @@
         <v>1218</v>
       </c>
       <c r="O301" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P301">
         <v>6600</v>
@@ -15772,7 +15775,7 @@
         <v>1218</v>
       </c>
       <c r="O302" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="P302">
         <v>6600</v>
@@ -15813,7 +15816,7 @@
         <v>368</v>
       </c>
       <c r="O303" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P303">
         <v>7100</v>
@@ -15823,11 +15826,11 @@
       <c r="A304" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="D304" t="s">
-        <v>1258</v>
+      <c r="D304" s="3" t="s">
+        <v>1467</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>1259</v>
+        <v>1468</v>
       </c>
       <c r="F304" s="2" t="s">
         <v>190</v>
@@ -15848,13 +15851,13 @@
         <v>22</v>
       </c>
       <c r="M304" s="3" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="N304" t="s">
         <v>368</v>
       </c>
       <c r="O304" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P304">
         <v>7100</v>
@@ -15862,13 +15865,13 @@
     </row>
     <row r="305" spans="1:16">
       <c r="A305" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>1261</v>
-      </c>
-      <c r="D305" t="s">
-        <v>1262</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>1263</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>190</v>
@@ -15889,13 +15892,13 @@
         <v>22</v>
       </c>
       <c r="M305" s="3" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="N305" t="s">
         <v>368</v>
       </c>
       <c r="O305" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P305">
         <v>7100</v>
@@ -15903,16 +15906,16 @@
     </row>
     <row r="306" spans="1:16">
       <c r="A306" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>1265</v>
       </c>
-      <c r="D306" t="s">
+      <c r="F306" s="2" t="s">
         <v>1266</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>1268</v>
       </c>
       <c r="G306" s="3" t="s">
         <v>1255</v>
@@ -15930,13 +15933,13 @@
         <v>22</v>
       </c>
       <c r="M306" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="N306" t="s">
         <v>368</v>
       </c>
       <c r="O306" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P306">
         <v>7100</v>
@@ -15944,13 +15947,13 @@
     </row>
     <row r="307" spans="1:16">
       <c r="A307" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="D307" t="s">
-        <v>1271</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>1272</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>114</v>
@@ -15971,13 +15974,13 @@
         <v>22</v>
       </c>
       <c r="M307" s="3" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="N307" t="s">
         <v>368</v>
       </c>
       <c r="O307" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P307">
         <v>7100</v>
@@ -15985,13 +15988,13 @@
     </row>
     <row r="308" spans="1:16">
       <c r="A308" s="2" t="s">
-        <v>1274</v>
+        <v>1469</v>
       </c>
       <c r="D308" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>190</v>
@@ -16012,13 +16015,13 @@
         <v>22</v>
       </c>
       <c r="M308" s="3" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="N308" t="s">
         <v>368</v>
       </c>
       <c r="O308" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P308">
         <v>7100</v>
@@ -16026,13 +16029,13 @@
     </row>
     <row r="309" spans="1:16">
       <c r="A309" s="2" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>66</v>
@@ -16053,13 +16056,13 @@
         <v>22</v>
       </c>
       <c r="M309" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N309" t="s">
         <v>368</v>
       </c>
       <c r="O309" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P309">
         <v>7100</v>
@@ -16067,13 +16070,13 @@
     </row>
     <row r="310" spans="1:16">
       <c r="A310" s="2" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>66</v>
@@ -16094,13 +16097,13 @@
         <v>22</v>
       </c>
       <c r="M310" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="N310" t="s">
         <v>368</v>
       </c>
       <c r="O310" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P310">
         <v>7100</v>
@@ -16108,13 +16111,13 @@
     </row>
     <row r="311" spans="1:16">
       <c r="A311" s="2" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="D311" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>190</v>
@@ -16135,13 +16138,13 @@
         <v>22</v>
       </c>
       <c r="M311" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="N311" t="s">
         <v>368</v>
       </c>
       <c r="O311" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P311">
         <v>7100</v>
@@ -16149,13 +16152,13 @@
     </row>
     <row r="312" spans="1:16">
       <c r="A312" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>190</v>
@@ -16176,13 +16179,13 @@
         <v>22</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="N312" t="s">
         <v>368</v>
       </c>
       <c r="O312" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P312">
         <v>7100</v>
@@ -16190,13 +16193,13 @@
     </row>
     <row r="313" spans="1:16">
       <c r="A313" s="2" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="D313" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>66</v>
@@ -16217,13 +16220,13 @@
         <v>22</v>
       </c>
       <c r="M313" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N313" t="s">
         <v>368</v>
       </c>
       <c r="O313" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P313">
         <v>7100</v>
@@ -16231,16 +16234,16 @@
     </row>
     <row r="314" spans="1:16">
       <c r="A314" s="2" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="G314" s="3" t="s">
         <v>1255</v>
@@ -16258,13 +16261,13 @@
         <v>22</v>
       </c>
       <c r="M314" s="3" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="N314" t="s">
         <v>368</v>
       </c>
       <c r="O314" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P314">
         <v>7100</v>
@@ -16272,13 +16275,13 @@
     </row>
     <row r="315" spans="1:16">
       <c r="A315" s="2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="D315" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="F315" s="2" t="s">
         <v>190</v>
@@ -16299,13 +16302,13 @@
         <v>22</v>
       </c>
       <c r="M315" s="3" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="N315" t="s">
         <v>368</v>
       </c>
       <c r="O315" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P315">
         <v>7100</v>
@@ -16313,16 +16316,16 @@
     </row>
     <row r="316" spans="1:16">
       <c r="A316" s="2" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="D316" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="G316" s="3" t="s">
         <v>1255</v>
@@ -16340,13 +16343,13 @@
         <v>22</v>
       </c>
       <c r="M316" s="3" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="N316" t="s">
         <v>368</v>
       </c>
       <c r="O316" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P316">
         <v>7100</v>
@@ -16354,13 +16357,13 @@
     </row>
     <row r="317" spans="1:16">
       <c r="A317" s="2" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="D317" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>190</v>
@@ -16381,13 +16384,13 @@
         <v>22</v>
       </c>
       <c r="M317" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N317" t="s">
         <v>368</v>
       </c>
       <c r="O317" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P317">
         <v>7100</v>
@@ -16395,16 +16398,16 @@
     </row>
     <row r="318" spans="1:16">
       <c r="A318" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F318" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="D318" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>1310</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>1311</v>
       </c>
       <c r="G318" s="3" t="s">
         <v>1255</v>
@@ -16422,13 +16425,13 @@
         <v>22</v>
       </c>
       <c r="M318" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N318" t="s">
         <v>368</v>
       </c>
       <c r="O318" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P318">
         <v>7100</v>
@@ -16436,13 +16439,13 @@
     </row>
     <row r="319" spans="1:16">
       <c r="A319" s="2" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>190</v>
@@ -16463,13 +16466,13 @@
         <v>22</v>
       </c>
       <c r="M319" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="N319" t="s">
         <v>368</v>
       </c>
       <c r="O319" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P319">
         <v>7100</v>
@@ -16477,13 +16480,13 @@
     </row>
     <row r="320" spans="1:16">
       <c r="A320" s="2" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="D320" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>190</v>
@@ -16504,13 +16507,13 @@
         <v>22</v>
       </c>
       <c r="M320" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="N320" t="s">
         <v>368</v>
       </c>
       <c r="O320" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P320">
         <v>7100</v>
@@ -16518,13 +16521,13 @@
     </row>
     <row r="321" spans="1:16">
       <c r="A321" s="2" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="D321" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>190</v>
@@ -16545,13 +16548,13 @@
         <v>22</v>
       </c>
       <c r="M321" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="N321" t="s">
         <v>368</v>
       </c>
       <c r="O321" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P321">
         <v>7100</v>
@@ -16559,13 +16562,13 @@
     </row>
     <row r="322" spans="1:16">
       <c r="A322" s="2" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="D322" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>190</v>
@@ -16586,13 +16589,13 @@
         <v>22</v>
       </c>
       <c r="M322" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="N322" t="s">
         <v>368</v>
       </c>
       <c r="O322" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P322">
         <v>7100</v>
@@ -16600,13 +16603,13 @@
     </row>
     <row r="323" spans="1:16">
       <c r="A323" s="2" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="D323" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="F323" s="2" t="s">
         <v>190</v>
@@ -16627,13 +16630,13 @@
         <v>22</v>
       </c>
       <c r="M323" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N323" t="s">
         <v>368</v>
       </c>
       <c r="O323" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P323">
         <v>7100</v>
@@ -16641,13 +16644,13 @@
     </row>
     <row r="324" spans="1:16">
       <c r="A324" s="2" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="D324" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>190</v>
@@ -16668,13 +16671,13 @@
         <v>22</v>
       </c>
       <c r="M324" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N324" t="s">
         <v>368</v>
       </c>
       <c r="O324" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P324">
         <v>7100</v>
@@ -16682,13 +16685,13 @@
     </row>
     <row r="325" spans="1:16">
       <c r="A325" s="2" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="D325" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>66</v>
@@ -16709,13 +16712,13 @@
         <v>22</v>
       </c>
       <c r="M325" s="3" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="N325" t="s">
         <v>368</v>
       </c>
       <c r="O325" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P325">
         <v>7100</v>
@@ -16723,13 +16726,13 @@
     </row>
     <row r="326" spans="1:16">
       <c r="A326" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="D326" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>564</v>
@@ -16750,13 +16753,13 @@
         <v>22</v>
       </c>
       <c r="M326" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="N326" t="s">
         <v>368</v>
       </c>
       <c r="O326" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P326">
         <v>7100</v>
@@ -16764,13 +16767,13 @@
     </row>
     <row r="327" spans="1:16">
       <c r="A327" s="2" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="D327" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="F327" s="2" t="s">
         <v>564</v>
@@ -16791,13 +16794,13 @@
         <v>22</v>
       </c>
       <c r="M327" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="N327" t="s">
         <v>368</v>
       </c>
       <c r="O327" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P327">
         <v>7100</v>
@@ -16805,13 +16808,13 @@
     </row>
     <row r="328" spans="1:16">
       <c r="A328" s="2" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="D328" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="F328" s="2" t="s">
         <v>190</v>
@@ -16836,7 +16839,7 @@
         <v>368</v>
       </c>
       <c r="O328" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P328">
         <v>7100</v>
@@ -16844,13 +16847,13 @@
     </row>
     <row r="329" spans="1:16">
       <c r="A329" s="2" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="D329" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>72</v>
@@ -16871,13 +16874,13 @@
         <v>22</v>
       </c>
       <c r="M329" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N329" t="s">
         <v>368</v>
       </c>
       <c r="O329" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P329">
         <v>7100</v>
@@ -16885,13 +16888,13 @@
     </row>
     <row r="330" spans="1:16">
       <c r="A330" s="2" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="D330" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>190</v>
@@ -16912,13 +16915,13 @@
         <v>22</v>
       </c>
       <c r="M330" s="3" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="N330" t="s">
         <v>368</v>
       </c>
       <c r="O330" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P330">
         <v>7100</v>
@@ -16926,13 +16929,13 @@
     </row>
     <row r="331" spans="1:16">
       <c r="A331" s="2" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="D331" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>66</v>
@@ -16953,13 +16956,13 @@
         <v>22</v>
       </c>
       <c r="M331" s="3" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="N331" t="s">
         <v>368</v>
       </c>
       <c r="O331" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P331">
         <v>7100</v>
@@ -16967,16 +16970,16 @@
     </row>
     <row r="332" spans="1:16">
       <c r="A332" s="2" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="D332" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="G332" s="3" t="s">
         <v>1255</v>
@@ -16994,13 +16997,13 @@
         <v>22</v>
       </c>
       <c r="M332" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="N332" t="s">
         <v>368</v>
       </c>
       <c r="O332" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P332">
         <v>7100</v>
@@ -17008,16 +17011,16 @@
     </row>
     <row r="333" spans="1:16">
       <c r="A333" s="2" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="D333" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="G333" s="3" t="s">
         <v>1255</v>
@@ -17035,13 +17038,13 @@
         <v>22</v>
       </c>
       <c r="M333" s="3" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="N333" t="s">
         <v>368</v>
       </c>
       <c r="O333" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P333">
         <v>7100</v>
@@ -17049,13 +17052,13 @@
     </row>
     <row r="334" spans="1:16">
       <c r="A334" s="2" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="D334" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>190</v>
@@ -17076,13 +17079,13 @@
         <v>22</v>
       </c>
       <c r="M334" s="3" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="N334" t="s">
         <v>368</v>
       </c>
       <c r="O334" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="P334">
         <v>7100</v>
@@ -31261,19 +31264,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E1" t="s">
         <v>1363</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>1364</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1367</v>
       </c>
       <c r="G1" t="s">
         <v>12</v>
@@ -31292,25 +31295,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D1" t="s">
         <v>1368</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>1369</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>1370</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>1371</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1374</v>
       </c>
     </row>
   </sheetData>
@@ -31326,16 +31329,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D1" t="s">
         <v>1375</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1378</v>
       </c>
     </row>
   </sheetData>
@@ -31374,7 +31377,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -31388,7 +31391,7 @@
         <v>334</v>
       </c>
       <c r="B3" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="C3">
         <v>200</v>
@@ -31402,7 +31405,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="C4">
         <v>300</v>
@@ -31416,13 +31419,13 @@
         <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="C5">
         <v>400</v>
       </c>
       <c r="D5" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -31430,13 +31433,13 @@
         <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="C6">
         <v>500</v>
       </c>
       <c r="D6" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -31444,13 +31447,13 @@
         <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="C7">
         <v>600</v>
       </c>
       <c r="D7" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -31458,7 +31461,7 @@
         <v>367</v>
       </c>
       <c r="B8" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="C8">
         <v>700</v>
@@ -31472,7 +31475,7 @@
         <v>277</v>
       </c>
       <c r="B9" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="C9">
         <v>800</v>
@@ -31483,7 +31486,7 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="C10">
         <v>900</v>
@@ -31494,7 +31497,7 @@
         <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="C11">
         <v>1000</v>
@@ -31505,7 +31508,7 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="C12">
         <v>1100</v>
@@ -31516,7 +31519,7 @@
         <v>319</v>
       </c>
       <c r="B13" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="C13">
         <v>1200</v>
@@ -31527,7 +31530,7 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="C14">
         <v>1300</v>
@@ -31535,7 +31538,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="B15" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="C15">
         <v>1400</v>
@@ -31543,7 +31546,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="B16" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="C16">
         <v>1500</v>
@@ -31551,7 +31554,7 @@
     </row>
     <row r="17" spans="2:3">
       <c r="B17" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="C17">
         <v>1600</v>
@@ -31559,7 +31562,7 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="C18">
         <v>1700</v>
@@ -31567,7 +31570,7 @@
     </row>
     <row r="19" spans="2:3">
       <c r="B19" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="C19">
         <v>1800</v>
@@ -31575,7 +31578,7 @@
     </row>
     <row r="20" spans="2:3">
       <c r="B20" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="C20">
         <v>1900</v>
@@ -31583,7 +31586,7 @@
     </row>
     <row r="21" spans="2:3">
       <c r="B21" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="C21">
         <v>2000</v>
@@ -31591,7 +31594,7 @@
     </row>
     <row r="22" spans="2:3">
       <c r="B22" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="C22">
         <v>2100</v>
@@ -31599,7 +31602,7 @@
     </row>
     <row r="23" spans="2:3">
       <c r="B23" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="C23">
         <v>2200</v>
@@ -31607,7 +31610,7 @@
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="C24">
         <v>2300</v>
@@ -31615,7 +31618,7 @@
     </row>
     <row r="25" spans="2:3">
       <c r="B25" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="C25">
         <v>2400</v>
@@ -31623,7 +31626,7 @@
     </row>
     <row r="26" spans="2:3">
       <c r="B26" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="C26">
         <v>2500</v>
@@ -31631,7 +31634,7 @@
     </row>
     <row r="27" spans="2:3">
       <c r="B27" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="C27">
         <v>2600</v>
@@ -31639,7 +31642,7 @@
     </row>
     <row r="28" spans="2:3">
       <c r="B28" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="C28">
         <v>2700</v>
@@ -31647,7 +31650,7 @@
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="C29">
         <v>2800</v>
@@ -31655,7 +31658,7 @@
     </row>
     <row r="30" spans="2:3">
       <c r="B30" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="C30">
         <v>2900</v>
@@ -31663,7 +31666,7 @@
     </row>
     <row r="31" spans="2:3">
       <c r="B31" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="C31">
         <v>3000</v>
@@ -31671,7 +31674,7 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="C32">
         <v>3100</v>
@@ -31679,7 +31682,7 @@
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="C33">
         <v>3200</v>
@@ -31687,7 +31690,7 @@
     </row>
     <row r="34" spans="2:3">
       <c r="B34" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="C34">
         <v>3300</v>
@@ -31695,7 +31698,7 @@
     </row>
     <row r="35" spans="2:3">
       <c r="B35" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="C35">
         <v>3400</v>
@@ -31703,7 +31706,7 @@
     </row>
     <row r="36" spans="2:3">
       <c r="B36" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="C36">
         <v>3500</v>
@@ -31711,7 +31714,7 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="C37">
         <v>3600</v>
@@ -31719,7 +31722,7 @@
     </row>
     <row r="38" spans="2:3">
       <c r="B38" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="C38">
         <v>3700</v>
@@ -31727,7 +31730,7 @@
     </row>
     <row r="39" spans="2:3">
       <c r="B39" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="C39">
         <v>3800</v>
@@ -31735,7 +31738,7 @@
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="C40">
         <v>3900</v>
@@ -31743,7 +31746,7 @@
     </row>
     <row r="41" spans="2:3">
       <c r="B41" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="C41">
         <v>4000</v>
@@ -31751,7 +31754,7 @@
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="C42">
         <v>4100</v>
@@ -31759,7 +31762,7 @@
     </row>
     <row r="43" spans="2:3">
       <c r="B43" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="C43">
         <v>4200</v>
@@ -31767,7 +31770,7 @@
     </row>
     <row r="44" spans="2:3">
       <c r="B44" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="C44">
         <v>4300</v>
@@ -31775,7 +31778,7 @@
     </row>
     <row r="45" spans="2:3">
       <c r="B45" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="C45">
         <v>4400</v>
@@ -31783,7 +31786,7 @@
     </row>
     <row r="46" spans="2:3">
       <c r="B46" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="C46">
         <v>4500</v>
@@ -31791,7 +31794,7 @@
     </row>
     <row r="47" spans="2:3">
       <c r="B47" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="C47">
         <v>4600</v>
@@ -31799,7 +31802,7 @@
     </row>
     <row r="48" spans="2:3">
       <c r="B48" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="C48">
         <v>4700</v>
@@ -31807,7 +31810,7 @@
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="C49">
         <v>4900</v>
@@ -31815,7 +31818,7 @@
     </row>
     <row r="50" spans="2:3">
       <c r="B50" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="C50">
         <v>5000</v>
@@ -31823,7 +31826,7 @@
     </row>
     <row r="51" spans="2:3">
       <c r="B51" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="C51">
         <v>5100</v>
@@ -31831,7 +31834,7 @@
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="C52">
         <v>5200</v>
@@ -31839,7 +31842,7 @@
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="C53">
         <v>5300</v>
@@ -31847,7 +31850,7 @@
     </row>
     <row r="54" spans="2:3">
       <c r="B54" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="C54">
         <v>5400</v>
@@ -31855,7 +31858,7 @@
     </row>
     <row r="55" spans="2:3">
       <c r="B55" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="C55">
         <v>5500</v>
@@ -31863,7 +31866,7 @@
     </row>
     <row r="56" spans="2:3">
       <c r="B56" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="C56">
         <v>5600</v>
@@ -31871,7 +31874,7 @@
     </row>
     <row r="57" spans="2:3">
       <c r="B57" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="C57">
         <v>5700</v>
@@ -31879,7 +31882,7 @@
     </row>
     <row r="58" spans="2:3">
       <c r="B58" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="C58">
         <v>5800</v>
@@ -31887,7 +31890,7 @@
     </row>
     <row r="59" spans="2:3">
       <c r="B59" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="C59">
         <v>5900</v>
@@ -31895,7 +31898,7 @@
     </row>
     <row r="60" spans="2:3">
       <c r="B60" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="C60">
         <v>6000</v>
@@ -31903,7 +31906,7 @@
     </row>
     <row r="61" spans="2:3">
       <c r="B61" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="C61">
         <v>6100</v>
@@ -31911,7 +31914,7 @@
     </row>
     <row r="62" spans="2:3">
       <c r="B62" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="C62">
         <v>6200</v>
@@ -31919,7 +31922,7 @@
     </row>
     <row r="63" spans="2:3">
       <c r="B63" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="C63">
         <v>6300</v>
@@ -31927,7 +31930,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="B64" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="C64">
         <v>6400</v>
@@ -31935,7 +31938,7 @@
     </row>
     <row r="65" spans="2:3">
       <c r="B65" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="C65">
         <v>6500</v>
@@ -31943,7 +31946,7 @@
     </row>
     <row r="66" spans="2:3">
       <c r="B66" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="C66">
         <v>6600</v>
@@ -31951,7 +31954,7 @@
     </row>
     <row r="67" spans="2:3">
       <c r="B67" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="C67">
         <v>6700</v>
@@ -31959,7 +31962,7 @@
     </row>
     <row r="68" spans="2:3">
       <c r="B68" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="C68">
         <v>6800</v>
@@ -31967,7 +31970,7 @@
     </row>
     <row r="69" spans="2:3">
       <c r="B69" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="C69">
         <v>6900</v>
@@ -31983,7 +31986,7 @@
     </row>
     <row r="71" spans="2:3">
       <c r="B71" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="C71">
         <v>7100</v>
@@ -31991,7 +31994,7 @@
     </row>
     <row r="72" spans="2:3">
       <c r="B72" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="C72">
         <v>7200</v>
@@ -31999,7 +32002,7 @@
     </row>
     <row r="73" spans="2:3">
       <c r="B73" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="C73">
         <v>7300</v>
@@ -32007,7 +32010,7 @@
     </row>
     <row r="74" spans="2:3">
       <c r="B74" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="C74">
         <v>7400</v>
@@ -32015,7 +32018,7 @@
     </row>
     <row r="75" spans="2:3">
       <c r="B75" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="C75">
         <v>7500</v>
@@ -32023,7 +32026,7 @@
     </row>
     <row r="76" spans="2:3">
       <c r="B76" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="C76">
         <v>7600</v>
@@ -32031,7 +32034,7 @@
     </row>
     <row r="77" spans="2:3">
       <c r="B77" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="C77">
         <v>7700</v>
@@ -32039,7 +32042,7 @@
     </row>
     <row r="78" spans="2:3">
       <c r="B78" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="C78">
         <v>7800</v>
@@ -32047,7 +32050,7 @@
     </row>
     <row r="79" spans="2:3">
       <c r="B79" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="C79">
         <v>7900</v>
@@ -32055,7 +32058,7 @@
     </row>
     <row r="80" spans="2:3">
       <c r="B80" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="C80">
         <v>8000</v>
